--- a/samples/networkchecker-report.xlsx
+++ b/samples/networkchecker-report.xlsx
@@ -61,7 +61,7 @@
     <x:t>Внешний IP</x:t>
   </x:si>
   <x:si>
-    <x:t>35.247.94.103</x:t>
+    <x:t>8.235.75.40</x:t>
   </x:si>
   <x:si>
     <x:t>Наблюдений по IP</x:t>
@@ -73,7 +73,7 @@
     <x:t>Начало</x:t>
   </x:si>
   <x:si>
-    <x:t>29.10.2026 15:31:10</x:t>
+    <x:t>29.10.2026 20:54:31</x:t>
   </x:si>
   <x:si>
     <x:t>Длительность</x:t>
@@ -259,7 +259,7 @@
     <x:t>Разные внешние порты для одного узла — симметричный NAT. Нормально для мобильных операторов, нетипично для домашнего Wi-Fi.</x:t>
   </x:si>
   <x:si>
-    <x:t>stun.l.google.com:19302=37294, stun.cloudflare.com:3478=60976, stun.sipnet.ru:3478=36968</x:t>
+    <x:t>stun.l.google.com:19302=40261, stun.cloudflare.com:3478=32892, stun.sipnet.ru:3478=36196</x:t>
   </x:si>
   <x:si>
     <x:t>UDP-транспорт работает</x:t>
@@ -1161,7 +1161,7 @@
         <x:v>1</x:v>
       </x:c>
       <x:c r="F10" s="0">
-        <x:v>2.1</x:v>
+        <x:v>2.2</x:v>
       </x:c>
       <x:c r="G10" s="0">
         <x:v>15</x:v>

--- a/samples/networkchecker-report.xlsx
+++ b/samples/networkchecker-report.xlsx
@@ -73,7 +73,7 @@
     <x:t>Начало</x:t>
   </x:si>
   <x:si>
-    <x:t>29.10.2026 20:54:31</x:t>
+    <x:t>29.10.2026 21:31:34</x:t>
   </x:si>
   <x:si>
     <x:t>Длительность</x:t>
@@ -259,7 +259,7 @@
     <x:t>Разные внешние порты для одного узла — симметричный NAT. Нормально для мобильных операторов, нетипично для домашнего Wi-Fi.</x:t>
   </x:si>
   <x:si>
-    <x:t>stun.l.google.com:19302=40261, stun.cloudflare.com:3478=32892, stun.sipnet.ru:3478=36196</x:t>
+    <x:t>stun.l.google.com:19302=38858, stun.cloudflare.com:3478=53376, stun.sipnet.ru:3478=55583</x:t>
   </x:si>
   <x:si>
     <x:t>UDP-транспорт работает</x:t>

--- a/samples/networkchecker-report.xlsx
+++ b/samples/networkchecker-report.xlsx
@@ -43,13 +43,13 @@
     <x:t>Что это значит</x:t>
   </x:si>
   <x:si>
-    <x:t>Признаков того, что трафик куда-то перенаправляют, не нашлось: ни туннелей, ни прокси, ни программ для обхода. Так выглядит обычное домашнее подключение.</x:t>
+    <x:t>В доступных данных не найдено признаков туннелей, прокси или программ обхода. Эти проверки не дают полной гарантии. Правда, 3 проверок пропущены или не смогли отработать — часть картины неизвестна.</x:t>
   </x:si>
   <x:si>
     <x:t>Что делать</x:t>
   </x:si>
   <x:si>
-    <x:t>Делать ничего не нужно. Если интернет работает медленно или что-то не открывается — причина не в VPN.</x:t>
+    <x:t>Если интернет работает медленно или что-то не открывается, нужны дополнительные проверки; этот результат не исключает VPN.</x:t>
   </x:si>
   <x:si>
     <x:t>Кратко</x:t>
@@ -73,13 +73,13 @@
     <x:t>Начало</x:t>
   </x:si>
   <x:si>
-    <x:t>29.10.2026 21:31:34</x:t>
+    <x:t>29.10.2026 21:54:24</x:t>
   </x:si>
   <x:si>
     <x:t>Длительность</x:t>
   </x:si>
   <x:si>
-    <x:t>2.2 с</x:t>
+    <x:t>2.5 с</x:t>
   </x:si>
   <x:si>
     <x:t>ОС</x:t>
@@ -259,7 +259,7 @@
     <x:t>Разные внешние порты для одного узла — симметричный NAT. Нормально для мобильных операторов, нетипично для домашнего Wi-Fi.</x:t>
   </x:si>
   <x:si>
-    <x:t>stun.l.google.com:19302=38858, stun.cloudflare.com:3478=53376, stun.sipnet.ru:3478=55583</x:t>
+    <x:t>stun.l.google.com:19302=58434, stun.cloudflare.com:3478=59428, stun.sipnet.ru:3478=38227</x:t>
   </x:si>
   <x:si>
     <x:t>UDP-транспорт работает</x:t>
@@ -1161,7 +1161,7 @@
         <x:v>1</x:v>
       </x:c>
       <x:c r="F10" s="0">
-        <x:v>2.2</x:v>
+        <x:v>2.5</x:v>
       </x:c>
       <x:c r="G10" s="0">
         <x:v>15</x:v>

--- a/samples/networkchecker-report.xlsx
+++ b/samples/networkchecker-report.xlsx
@@ -25,135 +25,138 @@
     <x:t>Вердикт</x:t>
   </x:si>
   <x:si>
-    <x:t>Признаков обхода не обнаружено</x:t>
+    <x:t>Требуется проверка</x:t>
   </x:si>
   <x:si>
     <x:t>Уровень</x:t>
   </x:si>
   <x:si>
+    <x:t>Требует проверки</x:t>
+  </x:si>
+  <x:si>
+    <x:t>Условный индекс</x:t>
+  </x:si>
+  <x:si>
+    <x:t>8 / 100</x:t>
+  </x:si>
+  <x:si>
+    <x:t>Что это значит</x:t>
+  </x:si>
+  <x:si>
+    <x:t>Нашлись мелочи, которые по отдельности ничего не значат: например, необычный адрес выхода или нестандартная настройка сети. Это не повод для паники, но и не идеально чистая картина. Правда, 7 проверок пропущены или не смогли отработать — часть картины неизвестна.</x:t>
+  </x:si>
+  <x:si>
+    <x:t>Что делать</x:t>
+  </x:si>
+  <x:si>
+    <x:t>Переключите тумблер «Подробно» и посмотрите, что помечено жёлтым. Если вы сами ничего не настраивали — такие сигналы могут иметь разные причины, в том числе настройки провайдера или роутера.</x:t>
+  </x:si>
+  <x:si>
+    <x:t>Кратко</x:t>
+  </x:si>
+  <x:si>
+    <x:t>Есть неоднозначные сигналы. Они могут иметь другие объяснения и не доказывают VPN, прокси или перехват. Индекс условный, не вероятность; влияние на браузер отдельно не проверялось.</x:t>
+  </x:si>
+  <x:si>
+    <x:t>Внешний IP</x:t>
+  </x:si>
+  <x:si>
+    <x:t>нет данных</x:t>
+  </x:si>
+  <x:si>
+    <x:t>Наблюдений по IP</x:t>
+  </x:si>
+  <x:si>
+    <x:t>0</x:t>
+  </x:si>
+  <x:si>
+    <x:t>Начало</x:t>
+  </x:si>
+  <x:si>
+    <x:t>29.10.2026 22:37:16</x:t>
+  </x:si>
+  <x:si>
+    <x:t>Длительность</x:t>
+  </x:si>
+  <x:si>
+    <x:t>0.0 с</x:t>
+  </x:si>
+  <x:si>
+    <x:t>ОС</x:t>
+  </x:si>
+  <x:si>
+    <x:t>Debian GNU/Linux 13 (trixie)</x:t>
+  </x:si>
+  <x:si>
+    <x:t>Компьютер</x:t>
+  </x:si>
+  <x:si>
+    <x:t>e2b</x:t>
+  </x:si>
+  <x:si>
+    <x:t>Приватный режим</x:t>
+  </x:si>
+  <x:si>
+    <x:t>выключен</x:t>
+  </x:si>
+  <x:si>
+    <x:t>Причины</x:t>
+  </x:si>
+  <x:si>
+    <x:t>•</x:t>
+  </x:si>
+  <x:si>
+    <x:t>Косвенные признаки: DNS-серверы туннельного интерфейса</x:t>
+  </x:si>
+  <x:si>
+    <x:t>Модуль</x:t>
+  </x:si>
+  <x:si>
+    <x:t>Что проверяли</x:t>
+  </x:si>
+  <x:si>
+    <x:t>Статус</x:t>
+  </x:si>
+  <x:si>
+    <x:t>Простыми словами</x:t>
+  </x:si>
+  <x:si>
+    <x:t>Находок</x:t>
+  </x:si>
+  <x:si>
+    <x:t>Время, с</x:t>
+  </x:si>
+  <x:si>
+    <x:t>Вес в вердикте</x:t>
+  </x:si>
+  <x:si>
+    <x:t>GeoIP и репутация IP</x:t>
+  </x:si>
+  <x:si>
+    <x:t>Смотрели, как ваш интернет-адрес выглядит со стороны</x:t>
+  </x:si>
+  <x:si>
+    <x:t>Пропущено</x:t>
+  </x:si>
+  <x:si>
+    <x:t>Не проверялось</x:t>
+  </x:si>
+  <x:si>
+    <x:t>Сравнение IP-источников</x:t>
+  </x:si>
+  <x:si>
+    <x:t>Сравнивали адрес, который видят разные сервисы</x:t>
+  </x:si>
+  <x:si>
+    <x:t>Прямые признаки</x:t>
+  </x:si>
+  <x:si>
+    <x:t>Искали включённые VPN, прокси и программы для обхода</x:t>
+  </x:si>
+  <x:si>
     <x:t>Чисто</x:t>
   </x:si>
   <x:si>
-    <x:t>Балл</x:t>
-  </x:si>
-  <x:si>
-    <x:t>5 / 100</x:t>
-  </x:si>
-  <x:si>
-    <x:t>Что это значит</x:t>
-  </x:si>
-  <x:si>
-    <x:t>В доступных данных не найдено признаков туннелей, прокси или программ обхода. Эти проверки не дают полной гарантии. Правда, 3 проверок пропущены или не смогли отработать — часть картины неизвестна.</x:t>
-  </x:si>
-  <x:si>
-    <x:t>Что делать</x:t>
-  </x:si>
-  <x:si>
-    <x:t>Если интернет работает медленно или что-то не открывается, нужны дополнительные проверки; этот результат не исключает VPN.</x:t>
-  </x:si>
-  <x:si>
-    <x:t>Кратко</x:t>
-  </x:si>
-  <x:si>
-    <x:t>Ни прямые, ни косвенные проверки не нашли следов туннеля, прокси или подмены.</x:t>
-  </x:si>
-  <x:si>
-    <x:t>Внешний IP</x:t>
-  </x:si>
-  <x:si>
-    <x:t>8.235.75.40</x:t>
-  </x:si>
-  <x:si>
-    <x:t>Наблюдений по IP</x:t>
-  </x:si>
-  <x:si>
-    <x:t>4</x:t>
-  </x:si>
-  <x:si>
-    <x:t>Начало</x:t>
-  </x:si>
-  <x:si>
-    <x:t>29.10.2026 21:54:24</x:t>
-  </x:si>
-  <x:si>
-    <x:t>Длительность</x:t>
-  </x:si>
-  <x:si>
-    <x:t>2.5 с</x:t>
-  </x:si>
-  <x:si>
-    <x:t>ОС</x:t>
-  </x:si>
-  <x:si>
-    <x:t>Debian GNU/Linux 13 (trixie)</x:t>
-  </x:si>
-  <x:si>
-    <x:t>Компьютер</x:t>
-  </x:si>
-  <x:si>
-    <x:t>e2b</x:t>
-  </x:si>
-  <x:si>
-    <x:t>Приватный режим</x:t>
-  </x:si>
-  <x:si>
-    <x:t>выключен</x:t>
-  </x:si>
-  <x:si>
-    <x:t>Причины</x:t>
-  </x:si>
-  <x:si>
-    <x:t>•</x:t>
-  </x:si>
-  <x:si>
-    <x:t>Косвенные признаки: DNS туннеля перекрывает системный</x:t>
-  </x:si>
-  <x:si>
-    <x:t>Модуль</x:t>
-  </x:si>
-  <x:si>
-    <x:t>Что проверяли</x:t>
-  </x:si>
-  <x:si>
-    <x:t>Статус</x:t>
-  </x:si>
-  <x:si>
-    <x:t>Простыми словами</x:t>
-  </x:si>
-  <x:si>
-    <x:t>Находок</x:t>
-  </x:si>
-  <x:si>
-    <x:t>Время, с</x:t>
-  </x:si>
-  <x:si>
-    <x:t>Вес в вердикте</x:t>
-  </x:si>
-  <x:si>
-    <x:t>GeoIP и репутация IP</x:t>
-  </x:si>
-  <x:si>
-    <x:t>Смотрели, как ваш интернет-адрес выглядит со стороны</x:t>
-  </x:si>
-  <x:si>
-    <x:t>Пропущено</x:t>
-  </x:si>
-  <x:si>
-    <x:t>Не проверялось</x:t>
-  </x:si>
-  <x:si>
-    <x:t>Сравнение IP-источников</x:t>
-  </x:si>
-  <x:si>
-    <x:t>Сравнивали адрес, который видят разные сервисы</x:t>
-  </x:si>
-  <x:si>
-    <x:t>Прямые признаки</x:t>
-  </x:si>
-  <x:si>
-    <x:t>Искали включённые VPN, прокси и программы для обхода</x:t>
-  </x:si>
-  <x:si>
     <x:t>Всё обычно</x:t>
   </x:si>
   <x:si>
@@ -163,9 +166,6 @@
     <x:t>Смотрели настройки сети: маршруты, DNS, размер пакетов</x:t>
   </x:si>
   <x:si>
-    <x:t>Требует проверки</x:t>
-  </x:si>
-  <x:si>
     <x:t>Есть мелочи</x:t>
   </x:si>
   <x:si>
@@ -235,52 +235,22 @@
     <x:t>внимание</x:t>
   </x:si>
   <x:si>
-    <x:t>DNS туннеля перекрывает системный</x:t>
-  </x:si>
-  <x:si>
-    <x:t>Туннельный адаптер публикует собственные DNS-серверы — трафик резолвинга идёт внутрь туннеля.</x:t>
+    <x:t>DNS-серверы туннельного интерфейса</x:t>
+  </x:si>
+  <x:si>
+    <x:t>Адаптер публикует DNS-серверы; фактический выбор зависит от маршрутов и политик DNS.</x:t>
   </x:si>
   <x:si>
     <x:t>8.8.8.8</x:t>
   </x:si>
   <x:si>
-    <x:t>Локальные прокси не обнаружены</x:t>
-  </x:si>
-  <x:si>
-    <x:t>На типовых портах (1080, 1087, 2080, 7890, 8080, 9050...) никто не ответил.</x:t>
-  </x:si>
-  <x:si>
-    <x:t>заметка</x:t>
-  </x:si>
-  <x:si>
-    <x:t>STUN-серверы видят разные порты</x:t>
-  </x:si>
-  <x:si>
-    <x:t>Разные внешние порты для одного узла — симметричный NAT. Нормально для мобильных операторов, нетипично для домашнего Wi-Fi.</x:t>
-  </x:si>
-  <x:si>
-    <x:t>stun.l.google.com:19302=58434, stun.cloudflare.com:3478=59428, stun.sipnet.ru:3478=38227</x:t>
-  </x:si>
-  <x:si>
-    <x:t>UDP-транспорт работает</x:t>
-  </x:si>
-  <x:si>
-    <x:t>Ответили 3 STUN-серверов. Голосовые вызовы и QUIC пойдут напрямую.</x:t>
-  </x:si>
-  <x:si>
-    <x:t>Все проверенные домены доступны</x:t>
-  </x:si>
-  <x:si>
-    <x:t>Ни DNS-, ни TCP-, ни TLS-блокировок не обнаружено. Если VPN активен, значит он не даёт заметного выигрыша по этим целям.</x:t>
-  </x:si>
-  <x:si>
-    <x:t>Задержки симметричны</x:t>
-  </x:si>
-  <x:si>
-    <x:t>Разница в пределах нормы: нет признаков «дальнего» маршрута до российских адресов.</x:t>
-  </x:si>
-  <x:si>
-    <x:t>Аномалий ICMP не обнаружено</x:t>
+    <x:t>Локальные сервисы на проверенных портах не ответили</x:t>
+  </x:si>
+  <x:si>
+    <x:t>Это не исключает прокси на других портах или с другой настройкой.</x:t>
+  </x:si>
+  <x:si>
+    <x:t>Внешние сетевые проверки отключены.</x:t>
   </x:si>
   <x:si>
     <x:t>Источник</x:t>
@@ -295,25 +265,7 @@
     <x:t>Примечание</x:t>
   </x:si>
   <x:si>
-    <x:t>STUN · stun.l.google.com</x:t>
-  </x:si>
-  <x:si>
-    <x:t>нет данных</x:t>
-  </x:si>
-  <x:si>
-    <x:t>UDP-выход</x:t>
-  </x:si>
-  <x:si>
-    <x:t>STUN · stun.cloudflare.com</x:t>
-  </x:si>
-  <x:si>
-    <x:t>STUN · stun.sipnet.ru</x:t>
-  </x:si>
-  <x:si>
-    <x:t>HTTPS (TCP) · ipify</x:t>
-  </x:si>
-  <x:si>
-    <x:t>TCP-путь</x:t>
+    <x:t>Наблюдений нет</x:t>
   </x:si>
 </x:sst>
 </file>
@@ -932,8 +884,7 @@
     <x:col min="2" max="2" width="66.567768" style="0" customWidth="1"/>
     <x:col min="3" max="3" width="11.853482" style="0" customWidth="1"/>
     <x:col min="4" max="4" width="15.853482" style="0" customWidth="1"/>
-    <x:col min="5" max="5" width="1.710625" style="0" customWidth="1"/>
-    <x:col min="6" max="6" width="3.567768" style="0" customWidth="1"/>
+    <x:col min="5" max="6" width="1.710625" style="0" customWidth="1"/>
     <x:col min="7" max="7" width="2.996339" style="0" customWidth="1"/>
   </x:cols>
   <x:sheetData>
@@ -1014,10 +965,10 @@
         <x:v>44</x:v>
       </x:c>
       <x:c r="C4" s="6" t="s">
-        <x:v>4</x:v>
+        <x:v>45</x:v>
       </x:c>
       <x:c r="D4" s="6" t="s">
-        <x:v>45</x:v>
+        <x:v>46</x:v>
       </x:c>
       <x:c r="E4" s="0">
         <x:v>1</x:v>
@@ -1031,13 +982,13 @@
     </x:row>
     <x:row r="5" spans="1:7">
       <x:c r="A5" s="0" t="s">
-        <x:v>46</x:v>
+        <x:v>47</x:v>
       </x:c>
       <x:c r="B5" s="0" t="s">
-        <x:v>47</x:v>
+        <x:v>48</x:v>
       </x:c>
       <x:c r="C5" s="7" t="s">
-        <x:v>48</x:v>
+        <x:v>4</x:v>
       </x:c>
       <x:c r="D5" s="7" t="s">
         <x:v>49</x:v>
@@ -1060,10 +1011,10 @@
         <x:v>51</x:v>
       </x:c>
       <x:c r="C6" s="6" t="s">
-        <x:v>4</x:v>
+        <x:v>45</x:v>
       </x:c>
       <x:c r="D6" s="6" t="s">
-        <x:v>45</x:v>
+        <x:v>46</x:v>
       </x:c>
       <x:c r="E6" s="0">
         <x:v>1</x:v>
@@ -1082,17 +1033,17 @@
       <x:c r="B7" s="0" t="s">
         <x:v>53</x:v>
       </x:c>
-      <x:c r="C7" s="6" t="s">
-        <x:v>4</x:v>
-      </x:c>
-      <x:c r="D7" s="6" t="s">
-        <x:v>45</x:v>
+      <x:c r="C7" s="0" t="s">
+        <x:v>39</x:v>
+      </x:c>
+      <x:c r="D7" s="0" t="s">
+        <x:v>40</x:v>
       </x:c>
       <x:c r="E7" s="0">
-        <x:v>2</x:v>
+        <x:v>1</x:v>
       </x:c>
       <x:c r="F7" s="0">
-        <x:v>0.3</x:v>
+        <x:v>0</x:v>
       </x:c>
       <x:c r="G7" s="0">
         <x:v>10</x:v>
@@ -1128,17 +1079,17 @@
       <x:c r="B9" s="0" t="s">
         <x:v>57</x:v>
       </x:c>
-      <x:c r="C9" s="6" t="s">
-        <x:v>4</x:v>
-      </x:c>
-      <x:c r="D9" s="6" t="s">
-        <x:v>45</x:v>
+      <x:c r="C9" s="0" t="s">
+        <x:v>39</x:v>
+      </x:c>
+      <x:c r="D9" s="0" t="s">
+        <x:v>40</x:v>
       </x:c>
       <x:c r="E9" s="0">
         <x:v>1</x:v>
       </x:c>
       <x:c r="F9" s="0">
-        <x:v>0.4</x:v>
+        <x:v>0</x:v>
       </x:c>
       <x:c r="G9" s="0">
         <x:v>10</x:v>
@@ -1151,17 +1102,17 @@
       <x:c r="B10" s="0" t="s">
         <x:v>59</x:v>
       </x:c>
-      <x:c r="C10" s="6" t="s">
-        <x:v>4</x:v>
-      </x:c>
-      <x:c r="D10" s="6" t="s">
-        <x:v>45</x:v>
+      <x:c r="C10" s="0" t="s">
+        <x:v>39</x:v>
+      </x:c>
+      <x:c r="D10" s="0" t="s">
+        <x:v>40</x:v>
       </x:c>
       <x:c r="E10" s="0">
         <x:v>1</x:v>
       </x:c>
       <x:c r="F10" s="0">
-        <x:v>2.5</x:v>
+        <x:v>0</x:v>
       </x:c>
       <x:c r="G10" s="0">
         <x:v>15</x:v>
@@ -1174,11 +1125,11 @@
       <x:c r="B11" s="0" t="s">
         <x:v>61</x:v>
       </x:c>
-      <x:c r="C11" s="6" t="s">
-        <x:v>4</x:v>
-      </x:c>
-      <x:c r="D11" s="6" t="s">
-        <x:v>45</x:v>
+      <x:c r="C11" s="0" t="s">
+        <x:v>39</x:v>
+      </x:c>
+      <x:c r="D11" s="0" t="s">
+        <x:v>40</x:v>
       </x:c>
       <x:c r="E11" s="0">
         <x:v>1</x:v>
@@ -1204,13 +1155,13 @@
   <x:sheetPr>
     <x:outlinePr summaryBelow="1" summaryRight="1"/>
   </x:sheetPr>
-  <x:dimension ref="A1:E12"/>
+  <x:dimension ref="A1:E11"/>
   <x:sheetFormatPr defaultRowHeight="15"/>
   <x:cols>
-    <x:col min="1" max="1" width="21.710625" style="0" customWidth="1"/>
+    <x:col min="1" max="1" width="21.567768" style="0" customWidth="1"/>
     <x:col min="2" max="2" width="5.710625" style="0" customWidth="1"/>
-    <x:col min="3" max="3" width="35.282054" style="0" customWidth="1"/>
-    <x:col min="4" max="4" width="121.282054" style="0" customWidth="1"/>
+    <x:col min="3" max="3" width="15.282054" style="0" customWidth="1"/>
+    <x:col min="4" max="4" width="38.996339" style="0" customWidth="1"/>
     <x:col min="5" max="5" width="9.140625" style="0" customWidth="1"/>
   </x:cols>
   <x:sheetData>
@@ -1284,7 +1235,7 @@
     </x:row>
     <x:row r="5" spans="1:5">
       <x:c r="A5" s="8" t="s">
-        <x:v>46</x:v>
+        <x:v>47</x:v>
       </x:c>
       <x:c r="B5" s="8" t="s">
         <x:v>71</x:v>
@@ -1317,34 +1268,34 @@
       </x:c>
     </x:row>
     <x:row r="7" spans="1:5">
-      <x:c r="A7" s="7" t="s">
+      <x:c r="A7" s="0" t="s">
         <x:v>52</x:v>
       </x:c>
-      <x:c r="B7" s="7" t="s">
+      <x:c r="B7" s="0" t="s">
+        <x:v>65</x:v>
+      </x:c>
+      <x:c r="C7" s="0" t="s">
+        <x:v>66</x:v>
+      </x:c>
+      <x:c r="D7" s="0" t="s">
         <x:v>77</x:v>
       </x:c>
-      <x:c r="C7" s="7" t="s">
-        <x:v>78</x:v>
-      </x:c>
-      <x:c r="D7" s="7" t="s">
-        <x:v>79</x:v>
-      </x:c>
-      <x:c r="E7" s="7" t="s">
-        <x:v>80</x:v>
+      <x:c r="E7" s="0" t="s">
+        <x:v>68</x:v>
       </x:c>
     </x:row>
     <x:row r="8" spans="1:5">
       <x:c r="A8" s="0" t="s">
-        <x:v>52</x:v>
+        <x:v>54</x:v>
       </x:c>
       <x:c r="B8" s="0" t="s">
         <x:v>65</x:v>
       </x:c>
       <x:c r="C8" s="0" t="s">
-        <x:v>81</x:v>
+        <x:v>66</x:v>
       </x:c>
       <x:c r="D8" s="0" t="s">
-        <x:v>82</x:v>
+        <x:v>68</x:v>
       </x:c>
       <x:c r="E8" s="0" t="s">
         <x:v>68</x:v>
@@ -1352,7 +1303,7 @@
     </x:row>
     <x:row r="9" spans="1:5">
       <x:c r="A9" s="0" t="s">
-        <x:v>54</x:v>
+        <x:v>56</x:v>
       </x:c>
       <x:c r="B9" s="0" t="s">
         <x:v>65</x:v>
@@ -1361,7 +1312,7 @@
         <x:v>66</x:v>
       </x:c>
       <x:c r="D9" s="0" t="s">
-        <x:v>68</x:v>
+        <x:v>77</x:v>
       </x:c>
       <x:c r="E9" s="0" t="s">
         <x:v>68</x:v>
@@ -1369,16 +1320,16 @@
     </x:row>
     <x:row r="10" spans="1:5">
       <x:c r="A10" s="0" t="s">
-        <x:v>56</x:v>
+        <x:v>58</x:v>
       </x:c>
       <x:c r="B10" s="0" t="s">
         <x:v>65</x:v>
       </x:c>
       <x:c r="C10" s="0" t="s">
-        <x:v>83</x:v>
+        <x:v>66</x:v>
       </x:c>
       <x:c r="D10" s="0" t="s">
-        <x:v>84</x:v>
+        <x:v>77</x:v>
       </x:c>
       <x:c r="E10" s="0" t="s">
         <x:v>68</x:v>
@@ -1386,35 +1337,18 @@
     </x:row>
     <x:row r="11" spans="1:5">
       <x:c r="A11" s="0" t="s">
-        <x:v>58</x:v>
+        <x:v>60</x:v>
       </x:c>
       <x:c r="B11" s="0" t="s">
         <x:v>65</x:v>
       </x:c>
       <x:c r="C11" s="0" t="s">
-        <x:v>85</x:v>
+        <x:v>66</x:v>
       </x:c>
       <x:c r="D11" s="0" t="s">
-        <x:v>86</x:v>
+        <x:v>77</x:v>
       </x:c>
       <x:c r="E11" s="0" t="s">
-        <x:v>68</x:v>
-      </x:c>
-    </x:row>
-    <x:row r="12" spans="1:5">
-      <x:c r="A12" s="0" t="s">
-        <x:v>60</x:v>
-      </x:c>
-      <x:c r="B12" s="0" t="s">
-        <x:v>65</x:v>
-      </x:c>
-      <x:c r="C12" s="0" t="s">
-        <x:v>87</x:v>
-      </x:c>
-      <x:c r="D12" s="0" t="s">
-        <x:v>68</x:v>
-      </x:c>
-      <x:c r="E12" s="0" t="s">
         <x:v>68</x:v>
       </x:c>
     </x:row>
@@ -1432,7 +1366,7 @@
   <x:sheetPr>
     <x:outlinePr summaryBelow="1" summaryRight="1"/>
   </x:sheetPr>
-  <x:dimension ref="A1:D5"/>
+  <x:dimension ref="A1:D2"/>
   <x:sheetFormatPr defaultRowHeight="15"/>
   <x:cols>
     <x:col min="1" max="4" width="9.140625" style="0" customWidth="1"/>
@@ -1440,72 +1374,21 @@
   <x:sheetData>
     <x:row r="1" spans="1:4" ht="20" customHeight="1">
       <x:c r="A1" s="4" t="s">
-        <x:v>88</x:v>
+        <x:v>78</x:v>
       </x:c>
       <x:c r="B1" s="5" t="s">
-        <x:v>89</x:v>
+        <x:v>79</x:v>
       </x:c>
       <x:c r="C1" s="5" t="s">
-        <x:v>90</x:v>
+        <x:v>80</x:v>
       </x:c>
       <x:c r="D1" s="5" t="s">
-        <x:v>91</x:v>
+        <x:v>81</x:v>
       </x:c>
     </x:row>
     <x:row r="2" spans="1:4">
       <x:c r="A2" s="0" t="s">
-        <x:v>92</x:v>
-      </x:c>
-      <x:c r="B2" s="0" t="s">
-        <x:v>14</x:v>
-      </x:c>
-      <x:c r="C2" s="0" t="s">
-        <x:v>93</x:v>
-      </x:c>
-      <x:c r="D2" s="0" t="s">
-        <x:v>94</x:v>
-      </x:c>
-    </x:row>
-    <x:row r="3" spans="1:4">
-      <x:c r="A3" s="0" t="s">
-        <x:v>95</x:v>
-      </x:c>
-      <x:c r="B3" s="0" t="s">
-        <x:v>14</x:v>
-      </x:c>
-      <x:c r="C3" s="0" t="s">
-        <x:v>93</x:v>
-      </x:c>
-      <x:c r="D3" s="0" t="s">
-        <x:v>94</x:v>
-      </x:c>
-    </x:row>
-    <x:row r="4" spans="1:4">
-      <x:c r="A4" s="0" t="s">
-        <x:v>96</x:v>
-      </x:c>
-      <x:c r="B4" s="0" t="s">
-        <x:v>14</x:v>
-      </x:c>
-      <x:c r="C4" s="0" t="s">
-        <x:v>93</x:v>
-      </x:c>
-      <x:c r="D4" s="0" t="s">
-        <x:v>94</x:v>
-      </x:c>
-    </x:row>
-    <x:row r="5" spans="1:4">
-      <x:c r="A5" s="0" t="s">
-        <x:v>97</x:v>
-      </x:c>
-      <x:c r="B5" s="0" t="s">
-        <x:v>14</x:v>
-      </x:c>
-      <x:c r="C5" s="0" t="s">
-        <x:v>93</x:v>
-      </x:c>
-      <x:c r="D5" s="0" t="s">
-        <x:v>98</x:v>
+        <x:v>82</x:v>
       </x:c>
     </x:row>
   </x:sheetData>
